--- a/excel/saudamini_handloom_Pune.xlsx
+++ b/excel/saudamini_handloom_Pune.xlsx
@@ -436,6 +436,7 @@
     <col width="16.57" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
